--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_187_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_187_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="M2" t="n">
         <v>8</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
         <v>16</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,16 +1335,16 @@
         <v>14</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17" t="n">
         <v>5</v>
@@ -1727,7 +1727,7 @@
         <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2315,16 +2315,16 @@
         <v>14</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X22" t="n">
         <v>5</v>
@@ -2514,13 +2514,13 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X23" t="n">
         <v>9</v>
@@ -2707,16 +2707,16 @@
         <v>10</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X24" t="n">
         <v>3</v>
@@ -3491,10 +3491,10 @@
         <v>30</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U28" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>115</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U30" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="V30" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="X30" t="n">
         <v>32</v>
@@ -4491,7 +4491,7 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -4690,10 +4690,10 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X37" t="n">
         <v>1</v>
@@ -5471,13 +5471,13 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X41" t="n">
         <v>5</v>
@@ -5664,10 +5664,10 @@
         <v>17</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -6588,16 +6588,16 @@
         <v>79</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X47" t="n">
         <v>32</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_187_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_187_EL.xlsx
@@ -674,10 +674,10 @@
         <v>8</v>
       </c>
       <c r="N2" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="O2" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="P2" t="n">
         <v>11</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>88.89</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>16</v>
       </c>
       <c r="N3" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="O3" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="P3" t="n">
         <v>5</v>
@@ -854,17 +854,17 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V3" t="n">
         <v>6</v>
       </c>
       <c r="W3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>80.00</t>
+          <t>52.94</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>26.09</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,14 +1347,14 @@
         <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA17" t="n">
@@ -1543,14 +1543,14 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA18" t="n">
@@ -1739,14 +1739,14 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA19" t="n">
@@ -2327,10 +2327,10 @@
         <v>2</v>
       </c>
       <c r="X22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
@@ -2523,10 +2523,10 @@
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Y23" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2719,10 +2719,10 @@
         <v>2</v>
       </c>
       <c r="X24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y28" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
@@ -3839,14 +3839,14 @@
         <v>6</v>
       </c>
       <c r="X30" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="Y30" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>76.5%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4304,10 +4304,10 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y35" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
@@ -4500,14 +4500,14 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y36" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA36" t="n">
@@ -4536,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
@@ -5284,14 +5284,14 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA40" t="n">
@@ -5480,14 +5480,14 @@
         <v>1</v>
       </c>
       <c r="X41" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y41" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA41" t="n">
@@ -5676,14 +5676,14 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA42" t="n">
@@ -6068,14 +6068,14 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y44" t="n">
         <v>6</v>
       </c>
-      <c r="Y44" t="n">
-        <v>9</v>
-      </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA44" t="n">
@@ -6600,14 +6600,14 @@
         <v>2</v>
       </c>
       <c r="X47" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="Y47" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="AA47" t="n">
@@ -6636,7 +6636,7 @@
         <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
@@ -6647,11 +6647,11 @@
         <v>6</v>
       </c>
       <c r="AK47" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL47" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
